--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>116200</v>
       </c>
       <c r="E8" s="3">
+        <v>103600</v>
+      </c>
+      <c r="F8" s="3">
         <v>91900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>93000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>126600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>103500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>48000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>48100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>62300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>49600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>62500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>31600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>71600</v>
       </c>
       <c r="E9" s="3">
+        <v>64500</v>
+      </c>
+      <c r="F9" s="3">
         <v>36100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>59100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>75700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>69300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>37900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>44600</v>
       </c>
       <c r="E10" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F10" s="3">
         <v>55800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>33900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>29300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>29300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>3300</v>
       </c>
       <c r="E12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F12" s="3">
         <v>2500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1600</v>
       </c>
       <c r="U12" s="3">
         <v>1600</v>
       </c>
       <c r="V12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W12" s="3">
         <v>-100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,139 +1161,145 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-400</v>
       </c>
       <c r="E14" s="3">
+        <v>400</v>
+      </c>
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-700</v>
       </c>
       <c r="N14" s="3">
         <v>-700</v>
       </c>
       <c r="O14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-10200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>19700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-5600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F15" s="3">
         <v>4200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>800</v>
       </c>
       <c r="P15" s="3">
         <v>800</v>
       </c>
       <c r="Q15" s="3">
+        <v>800</v>
+      </c>
+      <c r="R15" s="3">
         <v>900</v>
-      </c>
-      <c r="R15" s="3">
-        <v>800</v>
       </c>
       <c r="S15" s="3">
         <v>800</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="T15" s="3">
+        <v>800</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>1100</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>110900</v>
       </c>
       <c r="E17" s="3">
+        <v>98500</v>
+      </c>
+      <c r="F17" s="3">
         <v>62000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>90800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>109600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>93600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>65300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>73400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>42700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>37900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>5300</v>
       </c>
       <c r="E18" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F18" s="3">
         <v>29900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,209 +1512,216 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-7300</v>
       </c>
       <c r="E20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-16100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-14900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-21900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-13700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>2800</v>
       </c>
       <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>27600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-23100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>-2200</v>
       </c>
       <c r="E23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F23" s="3">
         <v>22300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-24300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
+      <c r="D24" s="3">
+        <v>400</v>
       </c>
       <c r="E24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-2700</v>
       </c>
       <c r="E26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F26" s="3">
         <v>27500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-22700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-4600</v>
       </c>
       <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>28100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>7300</v>
       </c>
       <c r="E32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F32" s="3">
         <v>7300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>16100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>14900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>21900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>13700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>21300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-4600</v>
       </c>
       <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>28100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-4600</v>
       </c>
       <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>28100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,139 +2831,143 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E41" s="3">
         <v>48100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>48200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>14600</v>
       </c>
       <c r="E42" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F42" s="3">
         <v>13100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>29600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>28800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>6100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5300</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
@@ -2887,505 +2977,529 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>158000</v>
+        <v>213200</v>
       </c>
       <c r="E43" s="3">
+        <v>196300</v>
+      </c>
+      <c r="F43" s="3">
         <v>197500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>205600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>168800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>132700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>136600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>111300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>88400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>92600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>78800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>78400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>68900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>81600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>62400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>62500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>75800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>87300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>138100</v>
       </c>
       <c r="E44" s="3">
+        <v>140400</v>
+      </c>
+      <c r="F44" s="3">
         <v>150900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>157600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>141900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>126000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>102400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>87300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>72600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>39100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>41700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>31900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>29300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>28500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>30800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>35300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>27600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>23200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>24100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>1100</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>395400</v>
+      </c>
+      <c r="E46" s="3">
         <v>397100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>421200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>451200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>363000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>297700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>297000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>272000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>263700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>211500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>193800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>185900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>173300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>164700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>152300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>129100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>108000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>98200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>110500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>120200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>43700</v>
       </c>
       <c r="E47" s="3">
+        <v>42300</v>
+      </c>
+      <c r="F47" s="3">
         <v>43300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>36900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>34600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>26700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>26800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>26400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>23500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>26900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>29100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>87100</v>
       </c>
       <c r="E48" s="3">
+        <v>85400</v>
+      </c>
+      <c r="F48" s="3">
         <v>79700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>77000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>77100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>49500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>45500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>42400</v>
       </c>
       <c r="R48" s="3">
         <v>42400</v>
       </c>
       <c r="S48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="T48" s="3">
         <v>41800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>40000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>285200</v>
       </c>
       <c r="E49" s="3">
+        <v>285900</v>
+      </c>
+      <c r="F49" s="3">
         <v>296800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>296900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>297000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>112800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>110400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>104900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>100800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>96100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>87600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>83400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>60800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>60900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>61700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>61800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>58200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>69400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>54900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>56700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,37 +3643,40 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>8200</v>
       </c>
       <c r="E52" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F52" s="3">
         <v>5700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3300</v>
       </c>
       <c r="M52" s="3">
         <v>3300</v>
@@ -3565,40 +3685,43 @@
         <v>3300</v>
       </c>
       <c r="O52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P52" s="3">
         <v>2800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>819700</v>
+      </c>
+      <c r="E54" s="3">
         <v>818100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>846800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>872900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>785300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>518200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>503600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>469600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>452300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>394600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>361200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>345700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>309500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>297600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>285600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>261600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>233100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>242500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>233100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>249700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,434 +3923,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>159100</v>
       </c>
       <c r="E57" s="3">
+        <v>150800</v>
+      </c>
+      <c r="F57" s="3">
         <v>149900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>165100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>137900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>125800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>106000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>60400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>57300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>55400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>54700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>42900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>105000</v>
       </c>
       <c r="E58" s="3">
+        <v>111500</v>
+      </c>
+      <c r="F58" s="3">
         <v>111000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>108500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>77500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>72700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>114800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>67400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>77500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>85900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>90100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>62500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>64400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>68300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>71700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>65600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>66500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>95200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>89900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>47500</v>
       </c>
       <c r="E59" s="3">
+        <v>36400</v>
+      </c>
+      <c r="F59" s="3">
         <v>41900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>311700</v>
+      </c>
+      <c r="E60" s="3">
         <v>298700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>302800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>330600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>243300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>222700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>255100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>180200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>202400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>168000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>157100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>165200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>127700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>130600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>125500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>139600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>136400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>116500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>144700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>159300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>134900</v>
       </c>
       <c r="E61" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F61" s="3">
         <v>152900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>162500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>164700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>97100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>91600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>140200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>113300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>98400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>75600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>101500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>84700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>80300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>40600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>40400</v>
       </c>
       <c r="E62" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F62" s="3">
         <v>56800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>73100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>62500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>487600</v>
+        <v>520700</v>
       </c>
       <c r="E66" s="3">
+        <v>519500</v>
+      </c>
+      <c r="F66" s="3">
         <v>545700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>600200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>504800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>390900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>415300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>385500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>378600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>326800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>300200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>284500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>263700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>251400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>240600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>214800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>203700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>195200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>196000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>224900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,8 +4985,11 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>330500</v>
+        <v>299000</v>
       </c>
       <c r="E76" s="3">
+        <v>298600</v>
+      </c>
+      <c r="F76" s="3">
         <v>301100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>272600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>280500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>127400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>88300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>84200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>73700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>67700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>61000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>61300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>46700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>47300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>37100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-4600</v>
       </c>
       <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>28100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,68 +5612,69 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="E83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1200</v>
       </c>
       <c r="S83" s="3">
         <v>1200</v>
       </c>
       <c r="T83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U83" s="3">
         <v>1500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,68 +6054,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>14700</v>
       </c>
       <c r="E89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F89" s="3">
         <v>2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>20700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,68 +6158,69 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-2500</v>
       </c>
       <c r="I91" s="3">
         <v>-2000</v>
       </c>
       <c r="J91" s="3">
-        <v>-2600</v>
+        <v>-2500</v>
       </c>
       <c r="K91" s="3">
         <v>-2600</v>
       </c>
       <c r="L91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-400</v>
       </c>
       <c r="R91" s="3">
         <v>-400</v>
       </c>
       <c r="S91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,68 +6378,71 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-8700</v>
       </c>
       <c r="E94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,26 +6482,27 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>-300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,68 +6776,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-27000</v>
       </c>
       <c r="E100" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>40200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>33200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6604,67 +6850,70 @@
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6675,68 +6924,71 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>-19800</v>
       </c>
       <c r="E102" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-10800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2500</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>8</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E8" s="3">
         <v>116200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>91900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>126600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>103500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>66400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>48000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>48100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>62300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>49600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>29600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E9" s="3">
         <v>71600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>59100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>75700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>69300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>55300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>49600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>33200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E10" s="3">
         <v>44600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>39100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>55800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>33900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>31500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>29300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>29300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1600</v>
       </c>
       <c r="V12" s="3">
         <v>1600</v>
       </c>
       <c r="W12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X12" s="3">
         <v>-100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,145 +1180,151 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-700</v>
       </c>
       <c r="O14" s="3">
         <v>-700</v>
       </c>
       <c r="P14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-10200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>19700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-5600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>800</v>
       </c>
       <c r="Q15" s="3">
         <v>800</v>
       </c>
       <c r="R15" s="3">
+        <v>800</v>
+      </c>
+      <c r="S15" s="3">
         <v>900</v>
-      </c>
-      <c r="S15" s="3">
-        <v>800</v>
       </c>
       <c r="T15" s="3">
         <v>800</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="U15" s="3">
+        <v>800</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W15" s="3">
         <v>1100</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
       <c r="X15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E17" s="3">
         <v>110900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>98500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>90800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>93600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>65300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>73400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>27100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E18" s="3">
         <v>5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,218 +1545,225 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-16100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-21900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>27600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-23100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-24300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-16800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-22700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>28100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E32" s="3">
         <v>7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>16100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>21900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>21300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,145 +2917,149 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E41" s="3">
         <v>28400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>48200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E42" s="3">
         <v>14600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>29600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>28800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5300</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
@@ -2980,526 +3069,550 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>225900</v>
+      </c>
+      <c r="E43" s="3">
         <v>213200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>196300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>197500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>205600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>168800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>132700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>136600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>111300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>88400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>92600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>78800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>78400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>68900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>81600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>62400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>62500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>75800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>87300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E44" s="3">
         <v>138100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>140400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>150900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>157600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>141900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>126000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>102400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>87300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>72600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>39100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>41700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>31900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>29300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>28500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>30800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>35300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>27600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>23200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>24100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
         <v>4600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E46" s="3">
         <v>395400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>397100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>421200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>451200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>363000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>297700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>297000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>263700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>211500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>193800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>185900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>173300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>164700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>152300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>129100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>108000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>98200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>110500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>120200</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E47" s="3">
         <v>43700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>42300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>36900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>34400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>27200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>26700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>26800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>26400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>23500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>27300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>29100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E48" s="3">
         <v>87100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>85400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>79700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>77000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>52400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>49300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>45400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>42400</v>
       </c>
       <c r="S48" s="3">
         <v>42400</v>
       </c>
       <c r="T48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="U48" s="3">
         <v>41800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>40000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>284900</v>
+      </c>
+      <c r="E49" s="3">
         <v>285200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>285900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>296800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>296900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>297000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>112800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>110400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>104900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>100800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>96100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>87600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>83400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>60800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>60900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>61700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>61800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>58200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>69400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>54900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>56700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,40 +3762,43 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3800</v>
-      </c>
-      <c r="M52" s="3">
-        <v>3300</v>
       </c>
       <c r="N52" s="3">
         <v>3300</v>
@@ -3688,40 +3807,43 @@
         <v>3300</v>
       </c>
       <c r="P52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>819500</v>
+      </c>
+      <c r="E54" s="3">
         <v>819700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>818100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>846800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>872900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>785300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>518200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>503600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>469600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>452300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>394600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>361200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>345700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>309500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>297600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>285600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>261600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>233100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>242500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>233100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>249700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,452 +4053,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E57" s="3">
         <v>159100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>150800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>149900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>165100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>137900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>125800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>106000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>114000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>60400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>57300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>51900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>55400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>54700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>42900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E58" s="3">
         <v>105000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>111500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>111000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>108500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>77500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>114800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>48900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>67400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>77500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>85900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>90100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>62500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>64400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>68300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>71700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>65600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>66500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>95200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>89900</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E59" s="3">
         <v>47500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>316800</v>
+      </c>
+      <c r="E60" s="3">
         <v>311700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>298700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>302800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>330600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>243300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>222700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>255100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>180200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>202400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>168000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>157100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>165200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>127700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>130600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>125500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>139600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>136400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>116500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>144700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>159300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E61" s="3">
         <v>134900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>145900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>152900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>162500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>164700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>97100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>91600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>140200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>113300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>97000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>98400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>75600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>101500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>84700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>80300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>40600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E62" s="3">
         <v>40400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>56800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>73100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>62500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>26800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E66" s="3">
         <v>520700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>519500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>545700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>600200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>504800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>390900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>415300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>385500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>378600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>326800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>284500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>263700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>251400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>240600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>214800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>203700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>195200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>196000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>224900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,8 +5158,11 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E76" s="3">
         <v>299000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>298600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>301100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>272600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>127400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>88300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>84200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>73700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>61000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>61300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>46700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>47300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>37100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24800</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,71 +5810,72 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1200</v>
       </c>
       <c r="T83" s="3">
         <v>1200</v>
       </c>
       <c r="U83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V83" s="3">
         <v>1500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,71 +6270,74 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E89" s="3">
         <v>14700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,71 +6378,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2600</v>
       </c>
       <c r="L91" s="3">
         <v>-2600</v>
       </c>
       <c r="M91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-400</v>
       </c>
       <c r="S91" s="3">
         <v>-400</v>
       </c>
       <c r="T91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,71 +6607,74 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,13 +6715,14 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -6498,14 +6731,14 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,71 +7021,74 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-27000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>40200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-22100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>12900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>33200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-17800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6853,70 +7098,73 @@
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -6927,71 +7175,74 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>37800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2500</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6999,6 +7250,9 @@
         <v>8</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,352 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>340400</v>
+      </c>
+      <c r="F8" s="3">
         <v>140300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>116200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>103600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>91900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>93000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>126600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>103500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>67400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>91100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>66400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>81100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>35500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>48000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>42100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>48100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>25700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>62300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>36300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>49600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>18700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>62500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>29600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>31600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>201600</v>
+      </c>
+      <c r="F9" s="3">
         <v>88700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>71600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>64500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>36100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>59100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>75700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>69300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>45800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>55300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>37900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>49600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>20900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>25100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>23100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>25300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>14900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>33000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>28300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>11000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>33200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>14500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>17000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>138800</v>
+      </c>
+      <c r="F10" s="3">
         <v>51600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>44600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>39100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>55800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>33900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>50900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>34200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>21600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>35800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>28500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>31500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>14600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>22900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>19000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>22800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>10800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>29300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>16000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>21300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>29300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>15100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>14600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1055,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>2200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2500</v>
       </c>
       <c r="H12" s="3">
         <v>2600</v>
       </c>
       <c r="I12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K12" s="3">
         <v>2200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>500</v>
-      </c>
-      <c r="S12" s="3">
-        <v>900</v>
-      </c>
-      <c r="T12" s="3">
-        <v>600</v>
       </c>
       <c r="U12" s="3">
         <v>900</v>
       </c>
       <c r="V12" s="3">
+        <v>600</v>
+      </c>
+      <c r="W12" s="3">
+        <v>900</v>
+      </c>
+      <c r="X12" s="3">
         <v>1600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>-100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,162 +1217,180 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-1600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-10200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>19700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>3800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>4600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>900</v>
       </c>
       <c r="T15" s="3">
         <v>800</v>
       </c>
       <c r="U15" s="3">
+        <v>900</v>
+      </c>
+      <c r="V15" s="3">
         <v>800</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W15" s="3">
+        <v>800</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1100</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>305100</v>
+      </c>
+      <c r="F17" s="3">
         <v>123500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>110900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>98500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>62000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>90800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>109600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>93600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>65300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>73400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>56300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>67300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>30800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>36500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>33700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>35400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>25100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>42700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>30100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>32400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>21100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>37900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>21400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>27100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F18" s="3">
         <v>16800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>5300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>5100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>29900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>17000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>9900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>17700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>10100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>11500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>12700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>19600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>17200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>24600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>8200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,212 +1612,226 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-9500</v>
       </c>
       <c r="G20" s="3">
         <v>-7300</v>
       </c>
       <c r="H20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J20" s="3">
         <v>-9900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-7700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-6100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-8200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-4300</v>
       </c>
       <c r="O20" s="3">
         <v>-5000</v>
       </c>
       <c r="P20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-4200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-3500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-16100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-14900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-21900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-21300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3">
         <v>14600</v>
       </c>
-      <c r="E21" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
-        <v>27600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>37600</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>13800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>11200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>11500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>7000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>17300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-8700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-23100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>300</v>
+      </c>
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
-        <v>400</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -1762,14 +1842,14 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="W22" s="3">
+        <v>400</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1777,162 +1857,180 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F23" s="3">
         <v>9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>22300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>9500</v>
-      </c>
-      <c r="M23" s="3">
-        <v>4900</v>
       </c>
       <c r="N23" s="3">
         <v>9500</v>
       </c>
       <c r="O23" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>16100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-10200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-24300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>18200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-16800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>6900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>8100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-1600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>27500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>12600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-22700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>11200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>28100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1200</v>
       </c>
       <c r="P27" s="3">
         <v>600</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R27" s="3">
+        <v>600</v>
+      </c>
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>11300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-21500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>6800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2604,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F32" s="3">
         <v>7200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>7300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>9500</v>
       </c>
       <c r="G32" s="3">
         <v>7300</v>
       </c>
       <c r="H32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J32" s="3">
         <v>9900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>7700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>6100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>8200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4300</v>
       </c>
       <c r="O32" s="3">
         <v>5000</v>
       </c>
       <c r="P32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R32" s="3">
         <v>5900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>4200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>3500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>16100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>14900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>21900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>6400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>13700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>21300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>28100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1200</v>
       </c>
       <c r="P33" s="3">
         <v>600</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R33" s="3">
+        <v>600</v>
+      </c>
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>11300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-21500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>6800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>28100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1200</v>
       </c>
       <c r="P35" s="3">
         <v>600</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R35" s="3">
+        <v>600</v>
+      </c>
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>11300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-21500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>6800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,701 +3090,757 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F41" s="3">
         <v>24400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>28400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>48100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>57700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>68600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>47400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>33500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>39000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>36400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>36600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>36000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>21600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>19100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>30000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>27200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>48200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>10600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>5500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4300</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F42" s="3">
         <v>17000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>14600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>12100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>18900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>11200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>27600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>16900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>29600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>28800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>6100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>5000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>4900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>4700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>5300</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>242200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>244200</v>
+      </c>
+      <c r="F43" s="3">
         <v>225900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>213200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>196300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>197500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>205600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>168800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>132700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>131100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>136600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>111300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>100900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>88400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>92600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>78800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>78400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>68900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>81600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>62400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>62500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>75800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>87300</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>129200</v>
+      </c>
+      <c r="F44" s="3">
         <v>123700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>138100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>140400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>150900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>157600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>141900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>126000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>102400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>87300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>72600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>61000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>39100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>41700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>31900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>29300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>28500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>30800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>35300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>27600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>23200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>24100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>22200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>8100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>37900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>17100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>15600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>4600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>419500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>408100</v>
+      </c>
+      <c r="F46" s="3">
         <v>392000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>395400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>397100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>421200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>451200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>363000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>297700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>297000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>272000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>263700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>211500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>193800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>185900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>173300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>164700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>152300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>129100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>108000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>98200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>110500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>120200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>44800</v>
+      </c>
+      <c r="F47" s="3">
         <v>44500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>43700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>42300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>43300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>43100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>44000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>41700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>39300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>36900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>34600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>34400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>32600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>27600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>27200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>26700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>26800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>26400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>23500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>27300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>26900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>29100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>87900</v>
+      </c>
+      <c r="F48" s="3">
         <v>88900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>87100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>85400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>79700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>77000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>77100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>62100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>52400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>50400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>49500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>49300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>43900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>45500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>45400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>42600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>42400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>42400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>41800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>43800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>40000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>42700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>286900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>286700</v>
+      </c>
+      <c r="F49" s="3">
         <v>284900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>285200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>285900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>296800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>296900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>297000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>112800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>110400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>104900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>100800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>96100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>87600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>83400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>60800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>60900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>61700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>61800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>58200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>69400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>54900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>56700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,85 +3999,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F52" s="3">
         <v>9300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>3300</v>
       </c>
       <c r="P52" s="3">
         <v>3300</v>
       </c>
       <c r="Q52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S52" s="3">
         <v>2800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>868800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>837000</v>
+      </c>
+      <c r="F54" s="3">
         <v>819500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>819700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>818100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>846800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>872900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>785300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>518200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>503600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>469600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>452300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>394600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>361200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>345700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>309500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>297600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>285600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>261600</v>
-      </c>
-      <c r="U54" s="3">
-        <v>233100</v>
-      </c>
-      <c r="V54" s="3">
-        <v>242500</v>
       </c>
       <c r="W54" s="3">
         <v>233100</v>
       </c>
       <c r="X54" s="3">
+        <v>242500</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>233100</v>
+      </c>
+      <c r="Z54" s="3">
         <v>249700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,470 +4314,508 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>168100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>167500</v>
+      </c>
+      <c r="F57" s="3">
         <v>164000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>159100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>150800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>149900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>165100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>137900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>125800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>123200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>106000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>114000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>72100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>60400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>62500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>54700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>57300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>51900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>55400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>54700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>40600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>39400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>42900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>147700</v>
+      </c>
+      <c r="F58" s="3">
         <v>117500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>105000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>111500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>111000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>108500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>77500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>72700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>114800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>48900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>67400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>77500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>85900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>90100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>62500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>64400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>68300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>71700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>65600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>66500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>95200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>89900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F59" s="3">
         <v>35300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>47500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>36400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>41900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>57000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>27900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>24100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>17100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>25300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>21000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>18400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>10800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>12600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>16100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>9400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>10100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>26500</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>327300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>335400</v>
+      </c>
+      <c r="F60" s="3">
         <v>316800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>311700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>298700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>302800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>330600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>243300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>222700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>255100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>180200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>202400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>168000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>157100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>165200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>127700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>130600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>125500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>139600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>136400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>116500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>144700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>159300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>123000</v>
+      </c>
+      <c r="F61" s="3">
         <v>119100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>134900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>145900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>152900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>162500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>164700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>97100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>91600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>140200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>113300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>97000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>98400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>75600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>101500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>84700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>80300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>40600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>33100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>37100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>16900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>18000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F62" s="3">
         <v>48400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>40400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>42900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>56800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>73100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>62500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>40200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>39800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>37900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>38800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>39200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>27400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>27200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>19200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>21500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>21000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>20300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>22100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>26800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>20700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>17500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>554900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>523700</v>
+      </c>
+      <c r="F66" s="3">
         <v>519000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>520700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>519500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>545700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>600200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>504800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>390900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>415300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>385500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>378600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>326800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>300200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>284500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>263700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>251400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>240600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>214800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>203700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>195200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>196000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>224900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,8 +5503,14 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5238,8 +5586,14 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>313900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>313300</v>
+      </c>
+      <c r="F76" s="3">
         <v>300500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>299000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>298600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>301100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>272600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>280500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>127400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>88300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>84200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>73700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>67700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>61000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>61300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>45800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>46200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>45000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>46700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>29400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>47300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>37100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>24800</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>28100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1200</v>
       </c>
       <c r="P81" s="3">
         <v>600</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R81" s="3">
+        <v>600</v>
+      </c>
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>11300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-21500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>6800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,76 +6207,78 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>4900</v>
       </c>
-      <c r="E83" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="3">
         <v>5500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1500</v>
       </c>
       <c r="W83" s="3">
         <v>1200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
+      <c r="X83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>1200</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
@@ -5888,8 +6286,14 @@
       <c r="AA83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>21100</v>
       </c>
-      <c r="E89" s="3">
-        <v>14700</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-8500</v>
       </c>
-      <c r="G89" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J89" s="3">
         <v>41200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-32400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-13700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>21300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-7500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>10600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>10900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>20700</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6406,58 +6848,64 @@
         <v>-2000</v>
       </c>
       <c r="K91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-22200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>2200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>4400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-19800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-6500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,35 +7182,37 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J96" s="3">
         <v>-300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -6793,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,153 +7510,165 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>-59900</v>
+      </c>
+      <c r="H100" s="3">
         <v>3300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>29600</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>40200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>12900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-22100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>15700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>12900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>33200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>10100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-8800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-14300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-17800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-7400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O101" s="3">
+        <v>800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S101" s="3">
+        <v>500</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U101" s="3">
+        <v>400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>100</v>
+      </c>
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>900</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>500</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7178,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4000</v>
       </c>
-      <c r="E102" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-9500</v>
       </c>
-      <c r="G102" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>24300</v>
+      </c>
+      <c r="J102" s="3">
         <v>21200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>13900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-20800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>37800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>5100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2500</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>124400</v>
+        <v>92600</v>
       </c>
       <c r="E8" s="3">
-        <v>340400</v>
+        <v>124300</v>
       </c>
       <c r="F8" s="3">
+        <v>84000</v>
+      </c>
+      <c r="G8" s="3">
         <v>140300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>116200</v>
       </c>
-      <c r="H8" s="3">
-        <v>103600</v>
-      </c>
       <c r="I8" s="3">
-        <v>91900</v>
+        <v>105100</v>
       </c>
       <c r="J8" s="3">
         <v>93000</v>
       </c>
       <c r="K8" s="3">
+        <v>93000</v>
+      </c>
+      <c r="L8" s="3">
         <v>126600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>103500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>91100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>48000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>48100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>25700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>62300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>49600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>62500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>31600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>76600</v>
+        <v>55400</v>
       </c>
       <c r="E9" s="3">
-        <v>201600</v>
+        <v>78200</v>
       </c>
       <c r="F9" s="3">
-        <v>88700</v>
+        <v>41200</v>
       </c>
       <c r="G9" s="3">
-        <v>71600</v>
+        <v>89500</v>
       </c>
       <c r="H9" s="3">
-        <v>64500</v>
+        <v>73400</v>
       </c>
       <c r="I9" s="3">
-        <v>36100</v>
+        <v>67000</v>
       </c>
       <c r="J9" s="3">
+        <v>36600</v>
+      </c>
+      <c r="K9" s="3">
         <v>59100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>75700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>55300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>49600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>25100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>28300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>33200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>17000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>47800</v>
+        <v>37200</v>
       </c>
       <c r="E10" s="3">
-        <v>138800</v>
+        <v>46100</v>
       </c>
       <c r="F10" s="3">
-        <v>51600</v>
+        <v>42800</v>
       </c>
       <c r="G10" s="3">
-        <v>44600</v>
+        <v>50800</v>
       </c>
       <c r="H10" s="3">
-        <v>39100</v>
+        <v>42800</v>
       </c>
       <c r="I10" s="3">
-        <v>55800</v>
+        <v>38100</v>
       </c>
       <c r="J10" s="3">
+        <v>56400</v>
+      </c>
+      <c r="K10" s="3">
         <v>33900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>29300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>29300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>15100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>14600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5300</v>
       </c>
       <c r="F12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L12" s="3">
         <v>2200</v>
       </c>
-      <c r="G12" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1600</v>
       </c>
       <c r="Y12" s="3">
         <v>1600</v>
       </c>
       <c r="Z12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA12" s="3">
         <v>-100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,163 +1240,169 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="L14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3">
-        <v>100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-700</v>
       </c>
       <c r="R14" s="3">
         <v>-700</v>
       </c>
       <c r="S14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>19700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5500</v>
       </c>
       <c r="F15" s="3">
         <v>3900</v>
       </c>
       <c r="G15" s="3">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="H15" s="3">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="I15" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="J15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K15" s="3">
         <v>4600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>800</v>
       </c>
       <c r="T15" s="3">
         <v>800</v>
       </c>
       <c r="U15" s="3">
+        <v>800</v>
+      </c>
+      <c r="V15" s="3">
         <v>900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>800</v>
       </c>
       <c r="W15" s="3">
         <v>800</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="X15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3">
         <v>1100</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>114900</v>
+        <v>89700</v>
       </c>
       <c r="E17" s="3">
-        <v>305100</v>
+        <v>114400</v>
       </c>
       <c r="F17" s="3">
-        <v>123500</v>
+        <v>71700</v>
       </c>
       <c r="G17" s="3">
-        <v>110900</v>
+        <v>125500</v>
       </c>
       <c r="H17" s="3">
-        <v>98500</v>
+        <v>112400</v>
       </c>
       <c r="I17" s="3">
-        <v>62000</v>
+        <v>99900</v>
       </c>
       <c r="J17" s="3">
+        <v>63500</v>
+      </c>
+      <c r="K17" s="3">
         <v>90800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>109600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>30100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>32400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>37900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>27100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="3">
-        <v>35300</v>
+        <v>9900</v>
       </c>
       <c r="F18" s="3">
-        <v>16800</v>
+        <v>12300</v>
       </c>
       <c r="G18" s="3">
-        <v>5300</v>
+        <v>14800</v>
       </c>
       <c r="H18" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="I18" s="3">
-        <v>29900</v>
+        <v>5200</v>
       </c>
       <c r="J18" s="3">
+        <v>29500</v>
+      </c>
+      <c r="K18" s="3">
         <v>2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>19600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,245 +1647,252 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15600</v>
+        <v>4400</v>
       </c>
       <c r="E20" s="3">
-        <v>-19200</v>
+        <v>8800</v>
       </c>
       <c r="F20" s="3">
-        <v>-7200</v>
+        <v>-3800</v>
       </c>
       <c r="G20" s="3">
-        <v>-7300</v>
+        <v>1400</v>
       </c>
       <c r="H20" s="3">
-        <v>-9500</v>
+        <v>-1000</v>
       </c>
       <c r="I20" s="3">
-        <v>-7300</v>
+        <v>4300</v>
       </c>
       <c r="J20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-9900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-16100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6600</v>
       </c>
       <c r="F21" s="3">
-        <v>14600</v>
+        <v>20000</v>
       </c>
       <c r="G21" s="3">
-        <v>-16600</v>
+        <v>17500</v>
       </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>8400</v>
       </c>
       <c r="I21" s="3">
-        <v>37600</v>
+        <v>4900</v>
       </c>
       <c r="J21" s="3">
+        <v>31100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7200</v>
       </c>
       <c r="F22" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>22300</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="O23" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P23" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="U23" s="3">
+        <v>4500</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="W23" s="3">
         <v>16100</v>
       </c>
-      <c r="F23" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>22300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>8900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="N23" s="3">
-        <v>9500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>4900</v>
-      </c>
-      <c r="P23" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>5600</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>4500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="V23" s="3">
-        <v>16100</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>18200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-3900</v>
+        <v>-1300</v>
       </c>
       <c r="E24" s="3">
-        <v>7700</v>
+        <v>-4000</v>
       </c>
       <c r="F24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G24" s="3">
         <v>8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2200</v>
+        <v>-6200</v>
       </c>
       <c r="E26" s="3">
-        <v>8400</v>
+        <v>-2100</v>
       </c>
       <c r="F26" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1600</v>
+        <v>-6400</v>
       </c>
       <c r="E27" s="3">
-        <v>4800</v>
+        <v>-1500</v>
       </c>
       <c r="F27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15600</v>
+        <v>-4400</v>
       </c>
       <c r="E32" s="3">
-        <v>19200</v>
+        <v>-8800</v>
       </c>
       <c r="F32" s="3">
-        <v>7200</v>
+        <v>3800</v>
       </c>
       <c r="G32" s="3">
-        <v>7300</v>
+        <v>-1400</v>
       </c>
       <c r="H32" s="3">
-        <v>9500</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="3">
-        <v>7300</v>
+        <v>-4300</v>
       </c>
       <c r="J32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K32" s="3">
         <v>9900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>16100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>21900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>13700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>21300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1600</v>
+        <v>-6400</v>
       </c>
       <c r="E33" s="3">
-        <v>4800</v>
+        <v>-1500</v>
       </c>
       <c r="F33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1600</v>
+        <v>-6400</v>
       </c>
       <c r="E35" s="3">
-        <v>4800</v>
+        <v>-1500</v>
       </c>
       <c r="F35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,163 +3178,167 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>44200</v>
+        <v>32300</v>
       </c>
       <c r="E41" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F41" s="3">
         <v>16400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>68600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>48200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10100</v>
+        <v>5900</v>
       </c>
       <c r="E42" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F42" s="3">
         <v>16500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14600</v>
       </c>
-      <c r="H42" s="3">
-        <v>12100</v>
-      </c>
       <c r="I42" s="3">
-        <v>13100</v>
+        <v>11900</v>
       </c>
       <c r="J42" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K42" s="3">
         <v>18900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>27600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>29600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>28800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5300</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
@@ -3258,589 +3348,613 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>242200</v>
+        <v>205700</v>
       </c>
       <c r="E43" s="3">
-        <v>244200</v>
+        <v>214400</v>
       </c>
       <c r="F43" s="3">
-        <v>225900</v>
+        <v>231500</v>
       </c>
       <c r="G43" s="3">
-        <v>213200</v>
+        <v>218000</v>
       </c>
       <c r="H43" s="3">
-        <v>196300</v>
+        <v>204500</v>
       </c>
       <c r="I43" s="3">
-        <v>197500</v>
+        <v>184000</v>
       </c>
       <c r="J43" s="3">
+        <v>185300</v>
+      </c>
+      <c r="K43" s="3">
         <v>205600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>168800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>132700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>136600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>88400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>92600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>78800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>78400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>68900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>81600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>62400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>62500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>75800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>87300</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>122800</v>
+        <v>119200</v>
       </c>
       <c r="E44" s="3">
-        <v>129200</v>
+        <v>126200</v>
       </c>
       <c r="F44" s="3">
-        <v>123700</v>
+        <v>131100</v>
       </c>
       <c r="G44" s="3">
-        <v>138100</v>
+        <v>124700</v>
       </c>
       <c r="H44" s="3">
-        <v>140400</v>
+        <v>139200</v>
       </c>
       <c r="I44" s="3">
-        <v>150900</v>
+        <v>140600</v>
       </c>
       <c r="J44" s="3">
+        <v>152900</v>
+      </c>
+      <c r="K44" s="3">
         <v>157600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>141900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>126000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>102400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>87300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>72600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>39100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>41700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>31900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>29300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>28500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>30800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>35300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>27600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>23200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>24100</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
-        <v>1800</v>
+        <v>10200</v>
       </c>
       <c r="F45" s="3">
-        <v>900</v>
+        <v>6800</v>
       </c>
       <c r="G45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>22200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P45" s="3">
+        <v>37900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R45" s="3">
+        <v>17100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>15600</v>
+      </c>
+      <c r="T45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V45" s="3">
+        <v>700</v>
+      </c>
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>22200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>8100</v>
-      </c>
-      <c r="O45" s="3">
-        <v>37900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>17100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>15600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U45" s="3">
-        <v>700</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>4600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>419500</v>
+        <v>377100</v>
       </c>
       <c r="E46" s="3">
-        <v>408100</v>
+        <v>408700</v>
       </c>
       <c r="F46" s="3">
+        <v>407200</v>
+      </c>
+      <c r="G46" s="3">
         <v>392000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>395400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>397100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>421200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>451200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>363000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>297700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>297000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>272000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>263700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>211500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>193800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>185900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>173300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>164700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>152300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>129100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>108000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>98200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>110500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>120200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>44200</v>
+        <v>40500</v>
       </c>
       <c r="E47" s="3">
-        <v>44800</v>
+        <v>40400</v>
       </c>
       <c r="F47" s="3">
-        <v>44500</v>
+        <v>42800</v>
       </c>
       <c r="G47" s="3">
-        <v>43700</v>
+        <v>42800</v>
       </c>
       <c r="H47" s="3">
-        <v>42300</v>
+        <v>41300</v>
       </c>
       <c r="I47" s="3">
-        <v>43300</v>
+        <v>39700</v>
       </c>
       <c r="J47" s="3">
+        <v>40300</v>
+      </c>
+      <c r="K47" s="3">
         <v>43100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>36900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>34600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>34400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>32600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>27600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>27200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>26700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>26800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>23500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>27300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>26900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>29100</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>85800</v>
+        <v>91900</v>
       </c>
       <c r="E48" s="3">
-        <v>87900</v>
+        <v>86200</v>
       </c>
       <c r="F48" s="3">
-        <v>88900</v>
+        <v>87300</v>
       </c>
       <c r="G48" s="3">
-        <v>87100</v>
+        <v>85100</v>
       </c>
       <c r="H48" s="3">
-        <v>85400</v>
+        <v>83400</v>
       </c>
       <c r="I48" s="3">
+        <v>81800</v>
+      </c>
+      <c r="J48" s="3">
         <v>79700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>77000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>77100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>45500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>42600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>42400</v>
       </c>
       <c r="V48" s="3">
         <v>42400</v>
       </c>
       <c r="W48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="X48" s="3">
         <v>41800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>42700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>286900</v>
+        <v>287900</v>
       </c>
       <c r="E49" s="3">
-        <v>286700</v>
+        <v>287100</v>
       </c>
       <c r="F49" s="3">
+        <v>286600</v>
+      </c>
+      <c r="G49" s="3">
         <v>284900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>285200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>285900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>296800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>296900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>297000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>112800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>110400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>104900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>100800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>96100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>87600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>83400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>60800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>60900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>61700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>61800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>58200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>69400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>54900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>56700</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,49 +4122,52 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>32400</v>
+        <v>18900</v>
       </c>
       <c r="E52" s="3">
-        <v>9500</v>
+        <v>18300</v>
       </c>
       <c r="F52" s="3">
-        <v>9300</v>
+        <v>2400</v>
       </c>
       <c r="G52" s="3">
-        <v>8200</v>
+        <v>5200</v>
       </c>
       <c r="H52" s="3">
-        <v>7300</v>
+        <v>5800</v>
       </c>
       <c r="I52" s="3">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="J52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>3300</v>
       </c>
       <c r="Q52" s="3">
         <v>3300</v>
@@ -4056,40 +4176,43 @@
         <v>3300</v>
       </c>
       <c r="S52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T52" s="3">
         <v>2800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>868800</v>
+        <v>827300</v>
       </c>
       <c r="E54" s="3">
-        <v>837000</v>
+        <v>850600</v>
       </c>
       <c r="F54" s="3">
+        <v>836100</v>
+      </c>
+      <c r="G54" s="3">
         <v>819500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>819700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>818100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>846800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>872900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>785300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>518200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>503600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>469600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>452300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>394600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>361200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>345700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>309500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>297600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>285600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>261600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>233100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>242500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>233100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>249700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,506 +4446,525 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>168100</v>
+        <v>144800</v>
       </c>
       <c r="E57" s="3">
-        <v>167500</v>
+        <v>162000</v>
       </c>
       <c r="F57" s="3">
-        <v>164000</v>
+        <v>161300</v>
       </c>
       <c r="G57" s="3">
-        <v>159100</v>
+        <v>160300</v>
       </c>
       <c r="H57" s="3">
-        <v>150800</v>
+        <v>153800</v>
       </c>
       <c r="I57" s="3">
-        <v>149900</v>
+        <v>146300</v>
       </c>
       <c r="J57" s="3">
+        <v>145200</v>
+      </c>
+      <c r="K57" s="3">
         <v>165100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>137900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>125800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>123200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>106000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>114000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>60400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>62500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>54700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>57300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>51900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>55400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>54700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>39400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>42900</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>139100</v>
+        <v>122400</v>
       </c>
       <c r="E58" s="3">
-        <v>147700</v>
+        <v>139900</v>
       </c>
       <c r="F58" s="3">
+        <v>146100</v>
+      </c>
+      <c r="G58" s="3">
         <v>117500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>105000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>111500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>111000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>108500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>77500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>72700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>114800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>67400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>77500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>85900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>90100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>62500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>64400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>68300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>71700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>65600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>66500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>95200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>89900</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20100</v>
+        <v>15300</v>
       </c>
       <c r="E59" s="3">
-        <v>20200</v>
+        <v>14700</v>
       </c>
       <c r="F59" s="3">
-        <v>35300</v>
+        <v>12500</v>
       </c>
       <c r="G59" s="3">
-        <v>47500</v>
+        <v>27200</v>
       </c>
       <c r="H59" s="3">
-        <v>36400</v>
+        <v>37700</v>
       </c>
       <c r="I59" s="3">
-        <v>41900</v>
+        <v>27800</v>
       </c>
       <c r="J59" s="3">
+        <v>35700</v>
+      </c>
+      <c r="K59" s="3">
         <v>57000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>26500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>327300</v>
+        <v>295900</v>
       </c>
       <c r="E60" s="3">
-        <v>335400</v>
+        <v>329500</v>
       </c>
       <c r="F60" s="3">
+        <v>333000</v>
+      </c>
+      <c r="G60" s="3">
         <v>316800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>311700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>298700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>302800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>330600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>243300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>222700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>255100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>180200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>202400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>168000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>157100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>165200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>127700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>130600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>125500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>139600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>136400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>116500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>144700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>159300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>130900</v>
+        <v>144200</v>
       </c>
       <c r="E61" s="3">
-        <v>123000</v>
+        <v>131100</v>
       </c>
       <c r="F61" s="3">
+        <v>109000</v>
+      </c>
+      <c r="G61" s="3">
         <v>119100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>134900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>145900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>152900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>91600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>140200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>113300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>97000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>98400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>75600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>101500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>84700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>80300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>40600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>18000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>61900</v>
+        <v>4600</v>
       </c>
       <c r="E62" s="3">
-        <v>30100</v>
+        <v>4100</v>
       </c>
       <c r="F62" s="3">
-        <v>48400</v>
+        <v>3500</v>
       </c>
       <c r="G62" s="3">
-        <v>40400</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>42900</v>
+        <v>4100</v>
       </c>
       <c r="I62" s="3">
-        <v>56800</v>
+        <v>5700</v>
       </c>
       <c r="J62" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K62" s="3">
         <v>73100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>39200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>19200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>26800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>20700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>554900</v>
+        <v>481200</v>
       </c>
       <c r="E66" s="3">
-        <v>523700</v>
+        <v>501100</v>
       </c>
       <c r="F66" s="3">
-        <v>519000</v>
+        <v>487600</v>
       </c>
       <c r="G66" s="3">
-        <v>520700</v>
+        <v>484300</v>
       </c>
       <c r="H66" s="3">
-        <v>519500</v>
+        <v>487100</v>
       </c>
       <c r="I66" s="3">
-        <v>545700</v>
+        <v>487600</v>
       </c>
       <c r="J66" s="3">
+        <v>512500</v>
+      </c>
+      <c r="K66" s="3">
         <v>600200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>504800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>390900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>415300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>385500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>378600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>326800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>300200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>284500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>263700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>251400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>240600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>214800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>203700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>195200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>196000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>224900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,31 +5680,34 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="E72" s="3">
-        <v>0</v>
+        <v>-10700</v>
       </c>
       <c r="F72" s="3">
-        <v>0</v>
+        <v>-9100</v>
       </c>
       <c r="G72" s="3">
-        <v>0</v>
+        <v>-18400</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
+        <v>-18500</v>
       </c>
       <c r="I72" s="3">
-        <v>0</v>
+        <v>-13900</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>-12200</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>313900</v>
+        <v>309500</v>
       </c>
       <c r="E76" s="3">
-        <v>313300</v>
+        <v>314000</v>
       </c>
       <c r="F76" s="3">
+        <v>313400</v>
+      </c>
+      <c r="G76" s="3">
         <v>300500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>299000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>298600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>301100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>272600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>280500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>127400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>88300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>84200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>73700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>67700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>61000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>61300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>37100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1600</v>
+        <v>-6400</v>
       </c>
       <c r="E81" s="3">
-        <v>4800</v>
+        <v>-1500</v>
       </c>
       <c r="F81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,80 +6407,81 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>4900</v>
+        <v>2200</v>
       </c>
       <c r="G83" s="3">
-        <v>-14600</v>
+        <v>2700</v>
       </c>
       <c r="H83" s="3">
-        <v>4400</v>
+        <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="J83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K83" s="3">
         <v>5500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1200</v>
       </c>
       <c r="W83" s="3">
         <v>1200</v>
       </c>
       <c r="X83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,80 +6921,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>23300</v>
       </c>
       <c r="F89" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="G89" s="3">
         <v>21100</v>
       </c>
-      <c r="G89" s="3">
-        <v>12100</v>
-      </c>
       <c r="H89" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I89" s="3">
         <v>-8500</v>
       </c>
-      <c r="I89" s="3">
-        <v>11100</v>
-      </c>
       <c r="J89" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K89" s="3">
         <v>41200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-32400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20700</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,80 +7041,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4700</v>
+        <v>-1300</v>
       </c>
       <c r="E91" s="3">
-        <v>-6000</v>
+        <v>-2000</v>
       </c>
       <c r="F91" s="3">
-        <v>-6600</v>
+        <v>-1700</v>
       </c>
       <c r="G91" s="3">
-        <v>-6100</v>
+        <v>-2100</v>
       </c>
       <c r="H91" s="3">
-        <v>-5000</v>
+        <v>-4000</v>
       </c>
       <c r="I91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2600</v>
       </c>
       <c r="O91" s="3">
         <v>-2600</v>
       </c>
       <c r="P91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-400</v>
       </c>
       <c r="V91" s="3">
         <v>-400</v>
       </c>
       <c r="W91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,80 +7297,83 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
       </c>
       <c r="F94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-18400</v>
       </c>
-      <c r="G94" s="3">
-        <v>17000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
-        <v>-22500</v>
-      </c>
       <c r="J94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-22200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,38 +7417,39 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L96" s="3">
         <v>-200</v>
       </c>
-      <c r="G96" s="3">
-        <v>500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,80 +7759,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5300</v>
       </c>
       <c r="F100" s="3">
+        <v>10900</v>
+      </c>
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-59900</v>
-      </c>
       <c r="H100" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="I100" s="3">
         <v>3300</v>
       </c>
-      <c r="I100" s="3">
-        <v>29600</v>
-      </c>
       <c r="J100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>33200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>10100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7599,79 +7845,82 @@
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1100</v>
       </c>
       <c r="F101" s="3">
-        <v>-7400</v>
+        <v>900</v>
       </c>
       <c r="G101" s="3">
-        <v>-3700</v>
+        <v>2000</v>
       </c>
       <c r="H101" s="3">
-        <v>-1100</v>
+        <v>3100</v>
       </c>
       <c r="I101" s="3">
-        <v>6100</v>
+        <v>2500</v>
       </c>
       <c r="J101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -7682,80 +7931,83 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>28100</v>
       </c>
       <c r="F102" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-34500</v>
-      </c>
       <c r="H102" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-9500</v>
       </c>
-      <c r="I102" s="3">
-        <v>24300</v>
-      </c>
       <c r="J102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="K102" s="3">
         <v>21200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>37800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>8</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E8" s="3">
         <v>92600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>124300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>84000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>140300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>116200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>105100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>93000</v>
       </c>
       <c r="K8" s="3">
         <v>93000</v>
       </c>
       <c r="L8" s="3">
+        <v>93000</v>
+      </c>
+      <c r="M8" s="3">
         <v>126600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>103500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>91100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>48000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>48100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>49600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>62500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>29600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>31600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E9" s="3">
         <v>55400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>78200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41200</v>
       </c>
-      <c r="G9" s="3">
-        <v>89500</v>
-      </c>
       <c r="H9" s="3">
+        <v>89900</v>
+      </c>
+      <c r="I9" s="3">
         <v>73400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>67000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>75700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>55300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>37900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>49600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>33000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>28300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>33200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E10" s="3">
         <v>37200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>42800</v>
       </c>
-      <c r="G10" s="3">
-        <v>50800</v>
-      </c>
       <c r="H10" s="3">
+        <v>50300</v>
+      </c>
+      <c r="I10" s="3">
         <v>42800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>56400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>29300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>29300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>15100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>14600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3600</v>
       </c>
       <c r="G12" s="3">
         <v>3600</v>
       </c>
       <c r="H12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I12" s="3">
         <v>4400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>900</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1600</v>
       </c>
       <c r="Z12" s="3">
         <v>1600</v>
       </c>
       <c r="AA12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB12" s="3">
         <v>-100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,143 +1288,146 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R14" s="3">
-        <v>-700</v>
       </c>
       <c r="S14" s="3">
         <v>-700</v>
       </c>
       <c r="T14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E15" s="3">
         <v>4400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>800</v>
       </c>
       <c r="U15" s="3">
         <v>800</v>
       </c>
       <c r="V15" s="3">
+        <v>800</v>
+      </c>
+      <c r="W15" s="3">
         <v>900</v>
-      </c>
-      <c r="W15" s="3">
-        <v>800</v>
       </c>
       <c r="X15" s="3">
         <v>800</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Y15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3">
         <v>1100</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E17" s="3">
         <v>89700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>114400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>125500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>112400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>99900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>63500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>90800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>67300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>35400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>32400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>27100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,254 +1680,261 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>1400</v>
-      </c>
       <c r="H20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20000</v>
       </c>
-      <c r="G21" s="3">
-        <v>17500</v>
-      </c>
       <c r="H21" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I21" s="3">
         <v>8400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E22" s="3">
         <v>6100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>7200</v>
       </c>
       <c r="F22" s="3">
         <v>7200</v>
       </c>
       <c r="G22" s="3">
-        <v>3800</v>
+        <v>7200</v>
       </c>
       <c r="H22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I22" s="3">
         <v>7000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-16800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>16100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>21900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>21300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,169 +3264,173 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E41" s="3">
         <v>32300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>44500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>30000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>27200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>48200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4300</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>27600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>29600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>28800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5300</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
@@ -3351,610 +3440,634 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E43" s="3">
         <v>205700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>214400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>231500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>218000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>204500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>184000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>185300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>205600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>168800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>132700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>131100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>136600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>111300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>88400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>92600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>78800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>78400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>68900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>81600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>62400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>62500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>75800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>87300</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E44" s="3">
         <v>119200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>126200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>131100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>124700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>139200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>140600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>152900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>157600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>141900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>126000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>102400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>87300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>72600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>39100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>41700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>31900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>29300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>30800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>35300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>27600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>23200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>24100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E45" s="3">
         <v>12200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>4600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>382600</v>
+      </c>
+      <c r="E46" s="3">
         <v>377100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>408700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>407200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>392000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>395400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>397100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>421200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>451200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>363000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>297700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>297000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>272000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>263700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>211500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>193800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>185900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>173300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>164700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>152300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>129100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>108000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>98200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>110500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>120200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E47" s="3">
         <v>40500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>42800</v>
       </c>
       <c r="G47" s="3">
         <v>42800</v>
       </c>
       <c r="H47" s="3">
+        <v>42800</v>
+      </c>
+      <c r="I47" s="3">
         <v>41300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>36900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>34600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>34400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>27600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>26700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>26400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>23500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>27300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>26900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>29100</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E48" s="3">
         <v>91900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>86200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>87300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>85100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>83400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>81800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>79700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>77000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>42400</v>
       </c>
       <c r="W48" s="3">
         <v>42400</v>
       </c>
       <c r="X48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="Y48" s="3">
         <v>41800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>43800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>40000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42700</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E49" s="3">
         <v>287900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>287100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>286600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>284900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>285200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>285900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>296800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>296900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>297000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>112800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>110400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>104900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>100800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>96100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>87600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>83400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>60800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>60900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>61700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>61800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>58200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>69400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>54900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>56700</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,52 +4241,55 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E52" s="3">
         <v>18900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>3300</v>
       </c>
       <c r="R52" s="3">
         <v>3300</v>
@@ -4179,40 +4298,43 @@
         <v>3300</v>
       </c>
       <c r="T52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>835200</v>
+      </c>
+      <c r="E54" s="3">
         <v>827300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>850600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>836100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>819500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>819700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>818100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>846800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>872900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>785300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>518200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>503600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>469600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>452300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>394600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>361200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>345700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>309500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>297600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>285600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>261600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>233100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>242500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>233100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>249700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,524 +4576,543 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E57" s="3">
         <v>144800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>162000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>161300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>160300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>153800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>146300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>145200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>165100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>137900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>125800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>123200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>106000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>114000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>72100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>60400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>62500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>54700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>51900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>55400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>54700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>42900</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E58" s="3">
         <v>122400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>139900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>146100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>117500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>105000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>111500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>111000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>108500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>77500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>72700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>114800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>67400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>77500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>85900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>90100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>62500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>64400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>68300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>71700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>65600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>66500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>95200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>89900</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>37700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>35700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>26500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>288800</v>
+      </c>
+      <c r="E60" s="3">
         <v>295900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>329500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>333000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>316800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>311700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>298700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>302800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>330600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>243300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>222700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>255100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>180200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>202400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>168000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>157100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>165200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>127700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>130600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>125500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>139600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>136400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>116500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>144700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>159300</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E61" s="3">
         <v>144200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>131100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>109000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>119100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>134900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>145900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>152900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>162500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>164700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>97100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>91600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>140200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>113300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>97000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>98400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>75600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>101500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>84700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>80300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>40600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>4600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3500</v>
       </c>
       <c r="G62" s="3">
         <v>3500</v>
       </c>
       <c r="H62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>19200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>26800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>17500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>488900</v>
+      </c>
+      <c r="E66" s="3">
         <v>481200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>501100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>487600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>484300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>487100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>487600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>512500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>600200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>504800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>390900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>415300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>385500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>378600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>326800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>300200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>284500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>263700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>251400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>240600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>214800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>203700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>195200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>196000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>224900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,35 +5853,38 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-16000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-18400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12200</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>309600</v>
+      </c>
+      <c r="E76" s="3">
         <v>309500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>314000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>313400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>299000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>298600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>301100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>272600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>280500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>127400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>88300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>84200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>73700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>67700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>61000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>37100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24800</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,83 +6605,84 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1200</v>
       </c>
       <c r="X83" s="3">
         <v>1200</v>
       </c>
       <c r="Y83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,83 +7137,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E89" s="3">
         <v>5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>41200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-32400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>20700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,83 +7261,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-4000</v>
       </c>
       <c r="I91" s="3">
         <v>-4000</v>
       </c>
       <c r="J91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-2600</v>
       </c>
       <c r="P91" s="3">
         <v>-2600</v>
       </c>
       <c r="Q91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-400</v>
       </c>
       <c r="W91" s="3">
         <v>-400</v>
       </c>
       <c r="X91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,83 +7526,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E94" s="3">
         <v>300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7444,15 +7677,15 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,83 +8004,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>12900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-22100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>15700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>12900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>33200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>10100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7848,82 +8093,85 @@
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -7934,83 +8182,86 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>21200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-20800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>37800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2500</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8018,6 +8269,9 @@
         <v>8</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E8" s="3">
         <v>106800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>92600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>124300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>116200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>105100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>93000</v>
       </c>
       <c r="L8" s="3">
         <v>93000</v>
       </c>
       <c r="M8" s="3">
+        <v>93000</v>
+      </c>
+      <c r="N8" s="3">
         <v>126600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>103500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>67400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>91100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>66400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>48000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>42100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>48100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>62300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>36300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>49600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>62500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>29600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>31600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E9" s="3">
         <v>63000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>78200</v>
       </c>
-      <c r="G9" s="3">
-        <v>41200</v>
-      </c>
       <c r="H9" s="3">
+        <v>41700</v>
+      </c>
+      <c r="I9" s="3">
         <v>89900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>73400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>67000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>59100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>75700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>55300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>37900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>49600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>23100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>33000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>28300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>33200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E10" s="3">
         <v>43800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>42300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>50300</v>
+      </c>
+      <c r="J10" s="3">
         <v>42800</v>
       </c>
-      <c r="H10" s="3">
-        <v>50300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>42800</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>56400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>35800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>29300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E12" s="3">
         <v>4100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5300</v>
       </c>
-      <c r="G12" s="3">
-        <v>3600</v>
-      </c>
       <c r="H12" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I12" s="3">
         <v>3800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1600</v>
       </c>
       <c r="AA12" s="3">
         <v>1600</v>
       </c>
       <c r="AB12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC12" s="3">
         <v>-100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,68 +1311,71 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-700</v>
       </c>
       <c r="T14" s="3">
         <v>-700</v>
       </c>
       <c r="U14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>19700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,77 +1383,77 @@
         <v>4300</v>
       </c>
       <c r="E15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>800</v>
       </c>
       <c r="V15" s="3">
         <v>800</v>
       </c>
       <c r="W15" s="3">
+        <v>800</v>
+      </c>
+      <c r="X15" s="3">
         <v>900</v>
-      </c>
-      <c r="X15" s="3">
-        <v>800</v>
       </c>
       <c r="Y15" s="3">
         <v>800</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="Z15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3">
         <v>1100</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
-      </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E17" s="3">
         <v>99200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>89700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>114400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>125500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>112400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>90800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>109600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>73400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>42700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>32400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>37900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>27100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>7600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,263 +1714,270 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-13700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-21300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E21" s="3">
         <v>11000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6600</v>
       </c>
-      <c r="G21" s="3">
-        <v>20000</v>
-      </c>
       <c r="H21" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I21" s="3">
         <v>16900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E22" s="3">
         <v>6300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7200</v>
       </c>
       <c r="G22" s="3">
         <v>7200</v>
       </c>
       <c r="H22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I22" s="3">
         <v>3200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-16800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-22700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
-        <v>3800</v>
-      </c>
       <c r="H32" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>16100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>14900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>21900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>13700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>21300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,175 +3351,179 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E41" s="3">
         <v>29200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>47400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>30000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>48200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4300</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>29600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>28800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5300</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
@@ -3443,631 +3533,655 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>198800</v>
+      </c>
+      <c r="E43" s="3">
         <v>237600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>205700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>214400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>231500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>218000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>204500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>184000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>185300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>205600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>168800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>132700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>131100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>136600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>88400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>92600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>78800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>78400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>68900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>81600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>62400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>62500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>75800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>87300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E44" s="3">
         <v>106200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>119200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>126200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>131100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>124700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>139200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>140600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>152900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>157600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>141900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>126000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>102400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>87300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>72600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>39100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>41700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>31900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>29300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>28500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>30800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>35300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>27600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>23200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>24100</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E45" s="3">
         <v>5500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>4600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>338200</v>
+      </c>
+      <c r="E46" s="3">
         <v>382600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>377100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>408700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>407200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>392000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>395400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>397100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>421200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>451200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>363000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>297700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>297000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>272000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>263700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>211500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>193800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>185900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>173300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>164700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>152300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>129100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>108000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>98200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>110500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>120200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E47" s="3">
         <v>40800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>42800</v>
       </c>
       <c r="H47" s="3">
         <v>42800</v>
       </c>
       <c r="I47" s="3">
+        <v>42800</v>
+      </c>
+      <c r="J47" s="3">
         <v>41300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>40300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>39300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>36900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>34600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>34400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>32600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>27200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>26800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>26400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>23500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>27300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>26900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>29100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E48" s="3">
         <v>91200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>91900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>86200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>87300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>85100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>83400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>81800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>79700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>42400</v>
       </c>
       <c r="X48" s="3">
         <v>42400</v>
       </c>
       <c r="Y48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="Z48" s="3">
         <v>41800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>43800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>40000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E49" s="3">
         <v>288500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>287900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>287100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>286600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>284900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>285200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>285900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>296800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>296900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>297000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>112800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>110400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>104900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>100800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>96100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>87600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>83400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>60800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>60900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>61700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>61800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>58200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>69400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>54900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>56700</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,55 +4361,58 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E52" s="3">
         <v>18600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>3300</v>
       </c>
       <c r="S52" s="3">
         <v>3300</v>
@@ -4301,40 +4421,43 @@
         <v>3300</v>
       </c>
       <c r="U52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>798200</v>
+      </c>
+      <c r="E54" s="3">
         <v>835200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>827300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>850600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>836100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>819500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>819700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>818100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>846800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>872900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>785300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>518200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>503600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>469600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>452300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>394600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>361200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>345700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>309500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>297600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>285600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>261600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>233100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>242500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>233100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>249700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4707,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E57" s="3">
         <v>136900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>144800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>162000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>161300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>160300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>153800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>146300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>145200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>165100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>137900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>125800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>123200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>106000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>114000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>72100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>60400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>62500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>54700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>51900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>55400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>54700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>40600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>39400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>42900</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>186700</v>
+      </c>
+      <c r="E58" s="3">
         <v>124500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>122400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>139900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>146100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>117500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>105000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>111500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>108500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>77500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>72700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>114800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>67400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>77500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>85900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>90100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>62500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>64400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>68300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>71700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>65600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>66500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>95200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>89900</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>37700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>57000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>26500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>332300</v>
+      </c>
+      <c r="E60" s="3">
         <v>288800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>295900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>329500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>333000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>316800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>311700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>298700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>302800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>330600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>243300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>222700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>255100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>180200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>202400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>168000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>157100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>165200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>127700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>130600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>125500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>139600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>136400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>116500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>144700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>159300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E61" s="3">
         <v>161200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>131100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>109000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>119100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>134900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>145900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>152900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>162500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>164700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>97100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>91600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>140200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>113300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>97000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>98400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>75600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>101500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>84700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>80300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>40600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3500</v>
       </c>
       <c r="H62" s="3">
         <v>3500</v>
       </c>
       <c r="I62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>73100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>62500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>39200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>27200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>20300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>17500</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>453200</v>
+      </c>
+      <c r="E66" s="3">
         <v>488900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>481200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>501100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>487600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>484300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>487100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>487600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>512500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>600200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>504800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>390900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>415300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>385500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>378600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>326800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>284500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>263700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>251400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>240600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>214800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>203700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>195200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>196000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>224900</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,38 +6027,41 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-16000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12200</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
       <c r="M72" s="3">
         <v>0</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>308500</v>
+      </c>
+      <c r="E76" s="3">
         <v>309600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>309500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>314000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>313400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>300500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>299000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>298600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>301100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>272600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>280500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>127400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>88300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>84200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>73700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>61300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>47300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>37100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6615,77 +6814,77 @@
         <v>2200</v>
       </c>
       <c r="E83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1200</v>
       </c>
       <c r="Y83" s="3">
         <v>1200</v>
       </c>
       <c r="Z83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,86 +7354,89 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>20700</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,86 +7482,87 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-4000</v>
       </c>
       <c r="J91" s="3">
         <v>-4000</v>
       </c>
       <c r="K91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-2600</v>
       </c>
       <c r="Q91" s="3">
         <v>-2600</v>
       </c>
       <c r="R91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-400</v>
       </c>
       <c r="X91" s="3">
         <v>-400</v>
       </c>
       <c r="Y91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,86 +7756,89 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7680,15 +7914,15 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,86 +8250,89 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E100" s="3">
         <v>6500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>12900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-22100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>15700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>12900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>33200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-17800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8096,85 +8342,88 @@
       <c r="AE100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8185,86 +8434,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-20800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>37800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2500</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>8</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>BIOX</t>
   </si>
@@ -656,429 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>77400</v>
+      </c>
+      <c r="F8" s="3">
         <v>74400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>59600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>106800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>92600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>124300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>84000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>140300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>105100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>93000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>93000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>126600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>103500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>67400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>91100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>66400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>81100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>35500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>48000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>42100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>48100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>25700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>62300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>36300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>49600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>18700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>62500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>29600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>31600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F9" s="3">
         <v>50800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>36800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>63000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>55400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>78200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>41700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>89900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>73400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>67000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>36600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>59100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>75700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>69300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>45800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>55300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>37900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>49600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>25100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>23100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>25300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>14900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>33000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>20300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>28300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>11000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>33200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>14500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>17000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F10" s="3">
         <v>23600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>22700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>43800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>37200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>46100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>42300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>50300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>42800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>38100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>56400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>33900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>50900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>34200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>21600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>35800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>28500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>31500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>14600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>22900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>19000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>22800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>10800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>29300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>16000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>21300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>29300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>15100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>14600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1137,111 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F12" s="3">
         <v>2700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>500</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>900</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>600</v>
       </c>
       <c r="AA12" s="3">
         <v>900</v>
       </c>
       <c r="AB12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD12" s="3">
         <v>1600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>-100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,32 +1335,38 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-7800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1337,163 +1376,175 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-700</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>19700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>4300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>5500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3600</v>
       </c>
       <c r="L15" s="3">
         <v>4100</v>
       </c>
       <c r="M15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O15" s="3">
         <v>3300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>3400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>3200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>800</v>
-      </c>
-      <c r="X15" s="3">
-        <v>800</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>900</v>
       </c>
       <c r="Z15" s="3">
         <v>800</v>
       </c>
       <c r="AA15" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3">
         <v>1100</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
-      </c>
       <c r="AF15" s="3">
         <v>0</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>70500</v>
+      </c>
+      <c r="F17" s="3">
         <v>95600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>57700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>99200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>89700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>114400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>71700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>125500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>112400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>99900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>63500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>90800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>109600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>93600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>65300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>73400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>56300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>67300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>30800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>36500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>33700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>35400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>25100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>42700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>30100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>32400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>21100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>37900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>21400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>27100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-21300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>9900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>12300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>14800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>29500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>17000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>9900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>17700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>11500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>12700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>19600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>6200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>24600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>8200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>4500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,266 +1814,280 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F20" s="3">
         <v>24300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-8200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-4300</v>
       </c>
       <c r="U20" s="3">
         <v>-5000</v>
       </c>
       <c r="V20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="X20" s="3">
         <v>-5900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-12600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-14900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-13700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-42100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>4900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>19500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>16900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>31100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>13800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>7300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>11200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>6900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>11500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>7000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>5600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>17300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F22" s="3">
         <v>7100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>6200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>6300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>6100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>7200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>5200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>400</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
@@ -2019,14 +2098,14 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2034,198 +2113,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-44900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>9600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>22300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>8900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
-      </c>
-      <c r="R23" s="3">
-        <v>9500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>4900</v>
       </c>
       <c r="T23" s="3">
         <v>9500</v>
       </c>
       <c r="U23" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V23" s="3">
+        <v>9500</v>
+      </c>
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-4400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>16100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-24300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>18200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-16800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F24" s="3">
         <v>6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>6900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>8100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>3400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>3500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>7000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-51700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>9800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>27500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-8400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>12600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-22700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>11200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-47900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>28100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>600</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-1200</v>
       </c>
       <c r="V27" s="3">
         <v>600</v>
       </c>
       <c r="W27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-7000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>11300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>6800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,13 +2719,19 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-178000</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-24300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>8200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>5000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>4300</v>
       </c>
       <c r="U32" s="3">
         <v>5000</v>
       </c>
       <c r="V32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="W32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="X32" s="3">
         <v>5900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>12600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>8200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>4200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>3500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>16100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>14900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>21900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>6400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>13700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>21300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-47900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>28100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
-      </c>
-      <c r="T33" s="3">
-        <v>600</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-1200</v>
       </c>
       <c r="V33" s="3">
         <v>600</v>
       </c>
       <c r="W33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-7000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>11300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>6800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-47900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>28100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
-      </c>
-      <c r="T35" s="3">
-        <v>600</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-1200</v>
       </c>
       <c r="V35" s="3">
         <v>600</v>
       </c>
       <c r="W35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-7000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>11300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>6800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,863 +3610,919 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F41" s="3">
         <v>32700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>38500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>29200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>32300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>44500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>24400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>28400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>48100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>57700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>68600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>47400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>33500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>39000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>36400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>36600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>36000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>21600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>19100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>30000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>27200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>48200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>10600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>5500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>6100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="F42" s="3">
         <v>2000</v>
       </c>
       <c r="G42" s="3">
+        <v>900</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I42" s="3">
         <v>5900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>16500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>17000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>14600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>12900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>18900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>5400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>3600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>5300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>11200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>27600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>16900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>29600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>28800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>6100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>5000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>4900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>4700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>5300</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
       <c r="AF42" s="3">
         <v>0</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>172200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>170400</v>
+      </c>
+      <c r="F43" s="3">
         <v>177500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>198800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>237600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>205700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>214400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>231500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>218000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>204500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>184000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>185300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>205600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>168800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>132700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>131100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>136600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>111300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>100900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>88400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>92600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>78800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>78400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>68900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>81600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>62400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>62500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>75800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>87300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F44" s="3">
         <v>90000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>93400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>106200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>119200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>126200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>131100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>124700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>139200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>140600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>152900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>157600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>141900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>126000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>102400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>87300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>72600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>61000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>39100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>41700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>31900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>29300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>28500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>30800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>35300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>27600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>23200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>24100</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>12200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>11200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>22200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>8100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>37900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>17100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>15600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>4600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>294300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>283200</v>
+      </c>
+      <c r="F46" s="3">
         <v>308300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>338200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>382600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>377100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>408700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>407200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>392000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>395400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>397100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>421200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>451200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>363000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>297700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>297000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>272000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>263700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>211500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>193800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>185900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>173300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>164700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>152300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>129100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>108000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>98200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>110500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>120200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E47" s="3">
         <v>39400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>39400</v>
+      </c>
+      <c r="G47" s="3">
         <v>39600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>40800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>40500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>40400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>42800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>42800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>41300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>39700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>40300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>43100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>44000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>41700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>39300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>36900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>34600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>34400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>32600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>27600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>27200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>26700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>26800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>26400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>23500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>27300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>26900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>29100</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F48" s="3">
         <v>91000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>92000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>91200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>91900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>86200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>87300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>85100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>83400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>81800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>79700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>77000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>77100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>62100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>52400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>50400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>49500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>49300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>43900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>45500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>45400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>42600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>42400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>42400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>41800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>43800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>40000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>42700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>290800</v>
+      </c>
+      <c r="F49" s="3">
         <v>293300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>294000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>288500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>287900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>289100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>286600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>284900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>285200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>285900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>296800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>296900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>297000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>112800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>110400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>104900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>100800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>96100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>87600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>83400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>60800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>60900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>61700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>61800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>58200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>69400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>54900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>56700</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="F52" s="3">
         <v>24000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>20200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>18600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>18900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>18300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>5800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="U52" s="3">
-        <v>3300</v>
       </c>
       <c r="V52" s="3">
         <v>3300</v>
       </c>
       <c r="W52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="X52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>560400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>734900</v>
+      </c>
+      <c r="F54" s="3">
         <v>763600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>798200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>835200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>827300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>852500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>836100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>819500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>819700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>818100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>846800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>872900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>785300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>518200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>503600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>469600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>452300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>394600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>361200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>345700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>309500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>297600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>285600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>261600</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>233100</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>242500</v>
       </c>
       <c r="AC54" s="3">
         <v>233100</v>
       </c>
       <c r="AD54" s="3">
+        <v>242500</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>233100</v>
+      </c>
+      <c r="AF54" s="3">
         <v>249700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +5098,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>89400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F57" s="3">
         <v>91900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>123900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>136900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>144800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>162000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>161300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>160300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>153800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>146300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>145200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>165100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>137900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>125800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>123200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>106000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>114000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>72100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>60400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>62500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>54700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>57300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>51900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>55400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>54700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>40600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>39400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>42900</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>191900</v>
+      </c>
+      <c r="F58" s="3">
         <v>228900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>186700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>124500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>122400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>139900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>146100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>117500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>105000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>111500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>111000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>108500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>77500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>72700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>114800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>48900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>67400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>77500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>85900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>90100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>62500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>64400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>68300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>71700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>65600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>66500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>95200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>89900</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F59" s="3">
         <v>7800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>15300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>14500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>27200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>37700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>27800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>35700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>57000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>27900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>24100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>17100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>25300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>21000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>18400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>10800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>10400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>5300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>16100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>9400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>10100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>26500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>328600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>299700</v>
+      </c>
+      <c r="F60" s="3">
         <v>338000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>332300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>288800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>295900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>329300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>333000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>316800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>311700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>298700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>302800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>330600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>243300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>222700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>255100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>180200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>202400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>168000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>157100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>165200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>127700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>130600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>125500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>139600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>136400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>116500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>144700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>159300</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>66600</v>
+      </c>
+      <c r="F61" s="3">
         <v>47700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>86600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>161200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>144200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>131100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>109000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>119100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>134900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>145900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>152900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>162500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>164700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>97100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>91600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>140200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>113300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>97000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>98400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>75600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>101500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>84700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>80300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>40600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>33100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>37100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>16900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>18000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>50200</v>
+      </c>
+      <c r="F62" s="3">
         <v>51200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>73100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>62500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>40200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>39800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>37900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>38800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>39200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>27400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>27200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>19200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>21500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>21000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>20300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>22100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>26800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>20700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>17500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>453700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>446500</v>
+      </c>
+      <c r="F66" s="3">
         <v>468400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>453200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>488900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>481200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>501200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>487600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>484300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>487100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>487600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>512500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>600200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>504800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>390900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>415300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>385500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>378600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>326800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>300200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>284500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>263700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>251400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>240600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>214800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>203700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>195200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>196000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>224900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,47 +6545,53 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-65000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-17200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-15900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-16000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-9600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-9100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-18400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-18500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-13900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-12200</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
@@ -6299,8 +6646,14 @@
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>258700</v>
+      </c>
+      <c r="F76" s="3">
         <v>265400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>308500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>309600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>309500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>315000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>313400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>300500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>299000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>298600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>301100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>272600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>280500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>127400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>88300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>84200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>73700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>67700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>61000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>61300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>45800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>46200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>45000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>46700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>29400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>47300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>37100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>24800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-47900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>28100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
-      </c>
-      <c r="T81" s="3">
-        <v>600</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-1200</v>
       </c>
       <c r="V81" s="3">
         <v>600</v>
       </c>
       <c r="W81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-7000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>11300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>6800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,94 +7399,96 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>5500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>4500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>3500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>1500</v>
       </c>
       <c r="AC83" s="3">
         <v>1200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
+      <c r="AD83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>1200</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
@@ -7099,8 +7496,14 @@
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F89" s="3">
         <v>26800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>23300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>23300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-17400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>21100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>14700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>41200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-32400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-6100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-13700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>21300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-16100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-7500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>5100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>10600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>10900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>20700</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2700</v>
       </c>
       <c r="G91" s="3">
         <v>-1300</v>
       </c>
       <c r="H91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-4900</v>
       </c>
       <c r="P91" s="3">
         <v>-2000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F94" s="3">
         <v>1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-18400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-22200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>2200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>4400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-19800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8154,18 +8621,18 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>-300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,189 +8984,201 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-25700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-12700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>6500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-18800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>10900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-27000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-10700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>40200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-22100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>15700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>12900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>33200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>10100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-7400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>3100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>2300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -8689,99 +9186,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>9300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-12200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>28100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-19700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>21200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>13900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>5900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-10700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>37800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
